--- a/docs/latets/CodePrompts/Sprint11/Lucky_test_prompts.xlsx
+++ b/docs/latets/CodePrompts/Sprint11/Lucky_test_prompts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\startup\VisibleAU\src\docs\latets\CodePrompts\Sprint6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\startup\VisibleAU\src\docs\latets\CodePrompts\Sprint11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54721873-178B-420A-8ADE-B92107341478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0C1A02-3A46-46EC-8075-3393FBDBCE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Status</t>
   </si>
@@ -92,18 +92,10 @@
   </si>
   <si>
     <t>Please analyse source code deep down from Sprint 1 - Sprint 6 for both backend databse and Api's, find out gaps in the end to end integration tests, fill the gaps, add new tests and fix any issues in the code using test data in the databse -</t>
-  </si>
-  <si>
-    <t>Please read through below document and complete the end to end tests for Sprint 6 backend databse and apis, fix any issues in the code-done
-C:\startup\VisibleAU\src\docs\latets\Sprints\e2e\Sprint6\s6-backend\CLAUDE.md</t>
   </si>
   <si>
     <t>Please read through below document and complete the end to end tests for Sprint 6 frontend  app, fix any issues in the code-done
 C:\startup\VisibleAU\src\docs\latets\Sprints\e2e\Sprint6\s6-frontend\CLAUDE.md</t>
-  </si>
-  <si>
-    <t>Please read through below document and create a batch scripts for each feature, the batch script should launch frontend app in the  browser and input real test data to complete end to end test for a feature, each feature should have it's own batch script launch a visible Chrome window and test. Could you please add 1 second which is configurable on top of each batch script, 1 second interval should be used for each input field entry, it should have 1 second delay before inputting on next input filed for demo purpose so that cleints can see what is happening on the screen
-C:\startup\VisibleAU\src\docs\latets\Sprints\qa\sprint6\SPRINT6-QA-FEATURE-DOC.md</t>
   </si>
 </sst>
 </file>
@@ -561,9 +553,6 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="12" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -645,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -673,9 +662,6 @@
     <row r="29" spans="1:2" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>19</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
